--- a/019-085-WENDLANDT-VENTAS/src/WendlandtVentas.Web/wwwroot/resources/Plantilla_Inventario.xlsx
+++ b/019-085-WENDLANDT-VENTAS/src/WendlandtVentas.Web/wwwroot/resources/Plantilla_Inventario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WENDLANDT SYS\Wend-Sys\019-085-WENDLANDT-VENTAS\src\WendlandtVentas.Web\wwwroot\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C314EA1-45EA-407C-AAA5-C86E53A6AD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A244D42-953B-44A5-87A4-5D7F5B788185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D50FD7-43D5-42D0-AAC0-11B39C34C376}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D50FD7-43D5-42D0-AAC0-11B39C34C376}"/>
   </bookViews>
   <sheets>
     <sheet name="02 MAR" sheetId="71" r:id="rId1"/>
@@ -705,7 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -851,15 +851,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -869,15 +860,33 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -895,38 +904,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -938,6 +918,8 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -951,6 +933,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1302,17 +1308,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
       <c r="J1" s="37"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -1363,11 +1369,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="60">
         <v>46083</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -1420,37 +1426,37 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="77" t="s">
+      <c r="C5" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="68"/>
-      <c r="H5" s="69" t="s">
+      <c r="G5" s="75"/>
+      <c r="H5" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="63" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
@@ -1463,25 +1469,25 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="80"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="68"/>
       <c r="F6" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
+      <c r="L6" s="59"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -1499,10 +1505,10 @@
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
-      <c r="D7" s="62"/>
+      <c r="D7" s="57"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="58"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="55"/>
       <c r="H7" s="10"/>
       <c r="I7" s="11"/>
       <c r="K7" s="2"/>
@@ -1528,9 +1534,9 @@
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
-      <c r="D8" s="62"/>
+      <c r="D8" s="57"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="61"/>
+      <c r="F8" s="56"/>
       <c r="G8" s="52"/>
       <c r="H8" s="10"/>
       <c r="I8" s="11"/>
@@ -1557,9 +1563,9 @@
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
-      <c r="D9" s="62"/>
+      <c r="D9" s="57"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="61"/>
+      <c r="F9" s="56"/>
       <c r="G9" s="52"/>
       <c r="H9" s="10"/>
       <c r="I9" s="11"/>
@@ -1586,9 +1592,9 @@
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
-      <c r="D10" s="62"/>
+      <c r="D10" s="57"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="61"/>
+      <c r="F10" s="56"/>
       <c r="G10" s="52"/>
       <c r="H10" s="10"/>
       <c r="I10" s="11"/>
@@ -1615,9 +1621,9 @@
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
-      <c r="D11" s="62"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="61"/>
+      <c r="F11" s="56"/>
       <c r="G11" s="52"/>
       <c r="H11" s="10"/>
       <c r="I11" s="11"/>
@@ -1644,9 +1650,9 @@
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
-      <c r="D12" s="62"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="61"/>
+      <c r="F12" s="56"/>
       <c r="G12" s="52"/>
       <c r="H12" s="10"/>
       <c r="I12" s="11"/>
@@ -1673,9 +1679,9 @@
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="62"/>
+      <c r="D13" s="57"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="61"/>
+      <c r="F13" s="56"/>
       <c r="G13" s="52"/>
       <c r="H13" s="10"/>
       <c r="I13" s="11"/>
@@ -1701,11 +1707,11 @@
         <v>36</v>
       </c>
       <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="54"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="93"/>
       <c r="H14" s="18"/>
       <c r="I14" s="20"/>
       <c r="K14" s="2"/>
@@ -1728,11 +1734,11 @@
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="53"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="95"/>
       <c r="H15" s="10"/>
       <c r="I15" s="11"/>
       <c r="K15" s="2"/>
@@ -1757,11 +1763,11 @@
         <v>37</v>
       </c>
       <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="53"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="95"/>
       <c r="H16" s="10"/>
       <c r="I16" s="11"/>
       <c r="K16" s="2"/>
@@ -1785,12 +1791,12 @@
       <c r="A17" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="55"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="96"/>
+      <c r="G17" s="97"/>
       <c r="H17" s="10"/>
       <c r="I17" s="11"/>
       <c r="K17" s="2"/>
@@ -1814,12 +1820,12 @@
       <c r="A18" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="62"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="24"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="56"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="53"/>
       <c r="H18" s="35"/>
       <c r="I18" s="11"/>
       <c r="K18" s="2"/>
@@ -1843,12 +1849,12 @@
       <c r="A19" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="62"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="57"/>
       <c r="E19" s="24"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="53"/>
       <c r="H19" s="35"/>
       <c r="I19" s="11"/>
       <c r="K19" s="2"/>
@@ -1872,12 +1878,12 @@
       <c r="A20" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="62"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="24"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="56"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="53"/>
       <c r="H20" s="35"/>
       <c r="I20" s="11"/>
       <c r="K20" s="2"/>
@@ -1901,11 +1907,11 @@
       <c r="A21" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="62"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="57"/>
       <c r="E21" s="24"/>
-      <c r="F21" s="61"/>
+      <c r="F21" s="56"/>
       <c r="G21" s="24"/>
       <c r="H21" s="35"/>
       <c r="I21" s="11"/>
@@ -8842,6 +8848,11 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="B3:D3"/>
@@ -8852,11 +8863,6 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -8885,18 +8891,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -8946,11 +8952,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="60">
         <v>46076</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -9005,48 +9011,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="69" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="63" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="87" t="s">
+      <c r="L5" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="69" t="s">
+      <c r="M5" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="69" t="s">
+      <c r="N5" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="69" t="s">
+      <c r="O5" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="69" t="s">
+      <c r="P5" s="63" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -9061,26 +9067,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -10470,13 +10476,13 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="89" t="s">
+      <c r="L36" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="84"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="83"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -10500,14 +10506,14 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="90">
+      <c r="L37" s="84">
         <f>P34-'03 FEB'!P33</f>
         <v>-3982.0700000000033</v>
       </c>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="92"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="85"/>
+      <c r="P37" s="86"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -10531,11 +10537,11 @@
       <c r="I38" s="29"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="84"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="83"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
@@ -10549,18 +10555,18 @@
     </row>
     <row r="39" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="95" t="s">
+      <c r="G39" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
       <c r="J39" s="30"/>
       <c r="K39" s="2"/>
       <c r="L39" s="31" t="s">
@@ -10591,18 +10597,18 @@
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
-      <c r="B40" s="85" t="s">
+      <c r="B40" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="85" t="s">
+      <c r="G40" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="32">
@@ -17000,6 +17006,16 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="G40:I40"/>
     <mergeCell ref="J5:J6"/>
@@ -17013,16 +17029,6 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -17051,18 +17057,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -17112,11 +17118,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="60">
         <v>46062</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -17171,48 +17177,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="69" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="63" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="87" t="s">
+      <c r="L5" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="69" t="s">
+      <c r="M5" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="69" t="s">
+      <c r="N5" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="69" t="s">
+      <c r="O5" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="69" t="s">
+      <c r="P5" s="63" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -17227,26 +17233,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -18690,13 +18696,13 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="89" t="s">
+      <c r="L37" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="84"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="83"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -18720,14 +18726,14 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="90">
+      <c r="L38" s="84">
         <f>P35-'03 FEB'!P33</f>
         <v>-4263.875</v>
       </c>
-      <c r="M38" s="91"/>
-      <c r="N38" s="91"/>
-      <c r="O38" s="91"/>
-      <c r="P38" s="92"/>
+      <c r="M38" s="85"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="85"/>
+      <c r="P38" s="86"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
@@ -18751,11 +18757,11 @@
       <c r="I39" s="29"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="83"/>
-      <c r="P39" s="84"/>
+      <c r="L39" s="87"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="82"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="83"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
@@ -18769,18 +18775,18 @@
     </row>
     <row r="40" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="95" t="s">
+      <c r="G40" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
       <c r="J40" s="30"/>
       <c r="K40" s="2"/>
       <c r="L40" s="31" t="s">
@@ -18811,18 +18817,18 @@
     </row>
     <row r="41" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="78"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="85" t="s">
+      <c r="G41" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
+      <c r="H41" s="78"/>
+      <c r="I41" s="78"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="32">
@@ -25220,6 +25226,16 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="G41:I41"/>
     <mergeCell ref="J5:J6"/>
@@ -25233,16 +25249,6 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -25271,18 +25277,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -25332,11 +25338,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="60">
         <v>46062</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -25391,48 +25397,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="69" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="63" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="87" t="s">
+      <c r="L5" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="69" t="s">
+      <c r="M5" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="69" t="s">
+      <c r="N5" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="69" t="s">
+      <c r="O5" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="69" t="s">
+      <c r="P5" s="63" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -25447,26 +25453,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -26840,13 +26846,13 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="89" t="s">
+      <c r="L36" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="84"/>
+      <c r="M36" s="82"/>
+      <c r="N36" s="82"/>
+      <c r="O36" s="82"/>
+      <c r="P36" s="83"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -26870,14 +26876,14 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="90">
+      <c r="L37" s="84">
         <f>P34-'03 FEB'!P33</f>
         <v>717.84500000000116</v>
       </c>
-      <c r="M37" s="91"/>
-      <c r="N37" s="91"/>
-      <c r="O37" s="91"/>
-      <c r="P37" s="92"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="85"/>
+      <c r="P37" s="86"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -26901,11 +26907,11 @@
       <c r="I38" s="29"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="93"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="84"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="82"/>
+      <c r="N38" s="82"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="83"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
@@ -26919,18 +26925,18 @@
     </row>
     <row r="39" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
-      <c r="B39" s="94" t="s">
+      <c r="B39" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="95" t="s">
+      <c r="G39" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
       <c r="J39" s="30"/>
       <c r="K39" s="2"/>
       <c r="L39" s="31" t="s">
@@ -26961,18 +26967,18 @@
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
-      <c r="B40" s="85" t="s">
+      <c r="B40" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="85" t="s">
+      <c r="G40" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="32">
@@ -33370,6 +33376,16 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="G40:I40"/>
     <mergeCell ref="J5:J6"/>
@@ -33383,16 +33399,6 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -33421,18 +33427,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="84"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -33482,11 +33488,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="73">
+      <c r="B3" s="60">
         <v>46056</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="75"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="62"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -33541,48 +33547,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="63" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="84"/>
-      <c r="G5" s="69" t="s">
+      <c r="F5" s="83"/>
+      <c r="G5" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="69" t="s">
+      <c r="H5" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="69" t="s">
+      <c r="I5" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="63" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="87" t="s">
+      <c r="L5" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="69" t="s">
+      <c r="M5" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="69" t="s">
+      <c r="N5" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="69" t="s">
+      <c r="O5" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="69" t="s">
+      <c r="P5" s="63" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -33597,26 +33603,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
-      <c r="D6" s="76"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="76"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
-      <c r="J6" s="76"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="88"/>
-      <c r="O6" s="88"/>
-      <c r="P6" s="88"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -34954,13 +34960,13 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="89" t="s">
+      <c r="L35" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="84"/>
+      <c r="M35" s="82"/>
+      <c r="N35" s="82"/>
+      <c r="O35" s="82"/>
+      <c r="P35" s="83"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
@@ -34984,14 +34990,14 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="90" t="e">
+      <c r="L36" s="84" t="e">
         <f>P33-#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M36" s="91"/>
-      <c r="N36" s="91"/>
-      <c r="O36" s="91"/>
-      <c r="P36" s="92"/>
+      <c r="M36" s="85"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="85"/>
+      <c r="P36" s="86"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -35015,11 +35021,11 @@
       <c r="I37" s="29"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="84"/>
+      <c r="L37" s="87"/>
+      <c r="M37" s="82"/>
+      <c r="N37" s="82"/>
+      <c r="O37" s="82"/>
+      <c r="P37" s="83"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -35033,18 +35039,18 @@
     </row>
     <row r="38" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
-      <c r="B38" s="94" t="s">
+      <c r="B38" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
+      <c r="C38" s="78"/>
+      <c r="D38" s="78"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="95" t="s">
+      <c r="G38" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
+      <c r="H38" s="78"/>
+      <c r="I38" s="78"/>
       <c r="J38" s="30"/>
       <c r="K38" s="2"/>
       <c r="L38" s="31" t="s">
@@ -35075,18 +35081,18 @@
     </row>
     <row r="39" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="85" t="s">
+      <c r="G39" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="32">
@@ -41484,6 +41490,16 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="J5:J6"/>
@@ -41497,16 +41513,6 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>

--- a/019-085-WENDLANDT-VENTAS/src/WendlandtVentas.Web/wwwroot/resources/Plantilla_Inventario.xlsx
+++ b/019-085-WENDLANDT-VENTAS/src/WendlandtVentas.Web/wwwroot/resources/Plantilla_Inventario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WENDLANDT SYS\Wend-Sys\019-085-WENDLANDT-VENTAS\src\WendlandtVentas.Web\wwwroot\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A244D42-953B-44A5-87A4-5D7F5B788185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CC804C-49AB-4824-923E-E59725EEA0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D50FD7-43D5-42D0-AAC0-11B39C34C376}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5D50FD7-43D5-42D0-AAC0-11B39C34C376}"/>
   </bookViews>
   <sheets>
     <sheet name="02 MAR" sheetId="71" r:id="rId1"/>
@@ -864,79 +864,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -957,6 +884,79 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1308,17 +1308,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
       <c r="J1" s="37"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -1369,11 +1369,9 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="60">
-        <v>46083</v>
-      </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -1426,37 +1424,37 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="74" t="s">
+      <c r="F5" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="75"/>
-      <c r="H5" s="63" t="s">
+      <c r="G5" s="70"/>
+      <c r="H5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="I5" s="71" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
@@ -1469,25 +1467,25 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="68"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="82"/>
       <c r="F6" s="51" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="59"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="59"/>
-      <c r="P6" s="59"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="74"/>
+      <c r="O6" s="74"/>
+      <c r="P6" s="74"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -1708,10 +1706,10 @@
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
-      <c r="D14" s="91"/>
+      <c r="D14" s="58"/>
       <c r="E14" s="18"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="93"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="18"/>
       <c r="I14" s="20"/>
       <c r="K14" s="2"/>
@@ -1735,10 +1733,10 @@
       <c r="A15" s="14"/>
       <c r="B15" s="10"/>
       <c r="C15" s="35"/>
-      <c r="D15" s="91"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="35"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="95"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="62"/>
       <c r="H15" s="10"/>
       <c r="I15" s="11"/>
       <c r="K15" s="2"/>
@@ -1764,10 +1762,10 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="35"/>
-      <c r="D16" s="91"/>
+      <c r="D16" s="58"/>
       <c r="E16" s="35"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="95"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="62"/>
       <c r="H16" s="10"/>
       <c r="I16" s="11"/>
       <c r="K16" s="2"/>
@@ -1793,10 +1791,10 @@
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="24"/>
-      <c r="D17" s="91"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="24"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="97"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="64"/>
       <c r="H17" s="10"/>
       <c r="I17" s="11"/>
       <c r="K17" s="2"/>
@@ -8848,11 +8846,6 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="B3:D3"/>
@@ -8863,6 +8856,11 @@
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="N5:N6"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -8891,18 +8889,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -8952,11 +8950,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="75">
         <v>46076</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -9011,48 +9009,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="74" t="s">
+      <c r="E5" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="63" t="s">
+      <c r="F5" s="86"/>
+      <c r="G5" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="I5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="63" t="s">
+      <c r="J5" s="71" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="M5" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N5" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O5" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="63" t="s">
+      <c r="P5" s="71" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -9067,26 +9065,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -10476,13 +10474,13 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="81" t="s">
+      <c r="L36" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="M36" s="82"/>
-      <c r="N36" s="82"/>
-      <c r="O36" s="82"/>
-      <c r="P36" s="83"/>
+      <c r="M36" s="85"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="85"/>
+      <c r="P36" s="86"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -10506,14 +10504,14 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="84">
+      <c r="L37" s="92">
         <f>P34-'03 FEB'!P33</f>
         <v>-3982.0700000000033</v>
       </c>
-      <c r="M37" s="85"/>
-      <c r="N37" s="85"/>
-      <c r="O37" s="85"/>
-      <c r="P37" s="86"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
+      <c r="O37" s="93"/>
+      <c r="P37" s="94"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -10537,11 +10535,11 @@
       <c r="I38" s="29"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="82"/>
-      <c r="N38" s="82"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="83"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="85"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="85"/>
+      <c r="P38" s="86"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
@@ -10555,18 +10553,18 @@
     </row>
     <row r="39" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="89" t="s">
+      <c r="G39" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88"/>
       <c r="J39" s="30"/>
       <c r="K39" s="2"/>
       <c r="L39" s="31" t="s">
@@ -10597,18 +10595,18 @@
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="77" t="s">
+      <c r="G40" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="32">
@@ -17006,16 +17004,6 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="G40:I40"/>
     <mergeCell ref="J5:J6"/>
@@ -17029,6 +17017,16 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -17057,18 +17055,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -17118,11 +17116,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="75">
         <v>46062</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -17177,48 +17175,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="74" t="s">
+      <c r="E5" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="63" t="s">
+      <c r="F5" s="86"/>
+      <c r="G5" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="I5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="63" t="s">
+      <c r="J5" s="71" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="M5" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N5" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O5" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="63" t="s">
+      <c r="P5" s="71" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -17233,26 +17231,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -18696,13 +18694,13 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="81" t="s">
+      <c r="L37" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="M37" s="82"/>
-      <c r="N37" s="82"/>
-      <c r="O37" s="82"/>
-      <c r="P37" s="83"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="85"/>
+      <c r="P37" s="86"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -18726,14 +18724,14 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="84">
+      <c r="L38" s="92">
         <f>P35-'03 FEB'!P33</f>
         <v>-4263.875</v>
       </c>
-      <c r="M38" s="85"/>
-      <c r="N38" s="85"/>
-      <c r="O38" s="85"/>
-      <c r="P38" s="86"/>
+      <c r="M38" s="93"/>
+      <c r="N38" s="93"/>
+      <c r="O38" s="93"/>
+      <c r="P38" s="94"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
@@ -18757,11 +18755,11 @@
       <c r="I39" s="29"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-      <c r="L39" s="87"/>
-      <c r="M39" s="82"/>
-      <c r="N39" s="82"/>
-      <c r="O39" s="82"/>
-      <c r="P39" s="83"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="85"/>
+      <c r="N39" s="85"/>
+      <c r="O39" s="85"/>
+      <c r="P39" s="86"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
@@ -18775,18 +18773,18 @@
     </row>
     <row r="40" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="89" t="s">
+      <c r="G40" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
       <c r="J40" s="30"/>
       <c r="K40" s="2"/>
       <c r="L40" s="31" t="s">
@@ -18817,18 +18815,18 @@
     </row>
     <row r="41" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
-      <c r="B41" s="77" t="s">
+      <c r="B41" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C41" s="78"/>
-      <c r="D41" s="78"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="88"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="77" t="s">
+      <c r="G41" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="H41" s="78"/>
-      <c r="I41" s="78"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="32">
@@ -25226,16 +25224,6 @@
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="G41:I41"/>
     <mergeCell ref="J5:J6"/>
@@ -25249,6 +25237,16 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -25277,18 +25275,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -25338,11 +25336,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="75">
         <v>46062</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -25397,48 +25395,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="74" t="s">
+      <c r="E5" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="63" t="s">
+      <c r="F5" s="86"/>
+      <c r="G5" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="I5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="63" t="s">
+      <c r="J5" s="71" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="M5" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N5" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O5" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="63" t="s">
+      <c r="P5" s="71" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -25453,26 +25451,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -26846,13 +26844,13 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="81" t="s">
+      <c r="L36" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="M36" s="82"/>
-      <c r="N36" s="82"/>
-      <c r="O36" s="82"/>
-      <c r="P36" s="83"/>
+      <c r="M36" s="85"/>
+      <c r="N36" s="85"/>
+      <c r="O36" s="85"/>
+      <c r="P36" s="86"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -26876,14 +26874,14 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="84">
+      <c r="L37" s="92">
         <f>P34-'03 FEB'!P33</f>
         <v>717.84500000000116</v>
       </c>
-      <c r="M37" s="85"/>
-      <c r="N37" s="85"/>
-      <c r="O37" s="85"/>
-      <c r="P37" s="86"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
+      <c r="O37" s="93"/>
+      <c r="P37" s="94"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -26907,11 +26905,11 @@
       <c r="I38" s="29"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="82"/>
-      <c r="N38" s="82"/>
-      <c r="O38" s="82"/>
-      <c r="P38" s="83"/>
+      <c r="L38" s="95"/>
+      <c r="M38" s="85"/>
+      <c r="N38" s="85"/>
+      <c r="O38" s="85"/>
+      <c r="P38" s="86"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
@@ -26925,18 +26923,18 @@
     </row>
     <row r="39" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="89" t="s">
+      <c r="G39" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88"/>
       <c r="J39" s="30"/>
       <c r="K39" s="2"/>
       <c r="L39" s="31" t="s">
@@ -26967,18 +26965,18 @@
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
+      <c r="C40" s="88"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-      <c r="G40" s="77" t="s">
+      <c r="G40" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="32">
@@ -33376,16 +33374,6 @@
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="G40:I40"/>
     <mergeCell ref="J5:J6"/>
@@ -33399,6 +33387,16 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
@@ -33427,18 +33425,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="86"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -33488,11 +33486,11 @@
       <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="75">
         <v>46056</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="77"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -33547,48 +33545,48 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="74" t="s">
+      <c r="E5" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="63" t="s">
+      <c r="F5" s="86"/>
+      <c r="G5" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="63" t="s">
+      <c r="H5" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="63" t="s">
+      <c r="I5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="63" t="s">
+      <c r="J5" s="71" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="63" t="s">
+      <c r="M5" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="N5" s="63" t="s">
+      <c r="N5" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="63" t="s">
+      <c r="O5" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="P5" s="63" t="s">
+      <c r="P5" s="71" t="s">
         <v>18</v>
       </c>
       <c r="Q5" s="2"/>
@@ -33603,26 +33601,26 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
+      <c r="L6" s="90"/>
+      <c r="M6" s="90"/>
+      <c r="N6" s="90"/>
+      <c r="O6" s="90"/>
+      <c r="P6" s="90"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -34960,13 +34958,13 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-      <c r="L35" s="81" t="s">
+      <c r="L35" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="M35" s="82"/>
-      <c r="N35" s="82"/>
-      <c r="O35" s="82"/>
-      <c r="P35" s="83"/>
+      <c r="M35" s="85"/>
+      <c r="N35" s="85"/>
+      <c r="O35" s="85"/>
+      <c r="P35" s="86"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
@@ -34990,14 +34988,14 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-      <c r="L36" s="84" t="e">
+      <c r="L36" s="92" t="e">
         <f>P33-#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M36" s="85"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
-      <c r="P36" s="86"/>
+      <c r="M36" s="93"/>
+      <c r="N36" s="93"/>
+      <c r="O36" s="93"/>
+      <c r="P36" s="94"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -35021,11 +35019,11 @@
       <c r="I37" s="29"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-      <c r="L37" s="87"/>
-      <c r="M37" s="82"/>
-      <c r="N37" s="82"/>
-      <c r="O37" s="82"/>
-      <c r="P37" s="83"/>
+      <c r="L37" s="95"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="85"/>
+      <c r="O37" s="85"/>
+      <c r="P37" s="86"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -35039,18 +35037,18 @@
     </row>
     <row r="38" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
-      <c r="B38" s="88" t="s">
+      <c r="B38" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="78"/>
-      <c r="D38" s="78"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="89" t="s">
+      <c r="G38" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="78"/>
-      <c r="I38" s="78"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="88"/>
       <c r="J38" s="30"/>
       <c r="K38" s="2"/>
       <c r="L38" s="31" t="s">
@@ -35081,18 +35079,18 @@
     </row>
     <row r="39" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
-      <c r="B39" s="77" t="s">
+      <c r="B39" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="78"/>
-      <c r="D39" s="78"/>
+      <c r="C39" s="88"/>
+      <c r="D39" s="88"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="77" t="s">
+      <c r="G39" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="32">
@@ -41490,16 +41488,6 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="I5:I6"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="G39:I39"/>
     <mergeCell ref="J5:J6"/>
@@ -41513,6 +41501,16 @@
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="O5:O6"/>
     <mergeCell ref="P5:P6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
